--- a/data/raw/OM.xlsx
+++ b/data/raw/OM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_0D12FA7D2C23FC90E8E5190A719AB67B9AC88E26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4F57C6-9873-43E7-B75C-FEC835345E63}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_0D12FA7D2C23FC90E8E5190A719AB67B9AC88E26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6851D289-20E8-4263-8B1F-4D15D6F25DE6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1090,7 +1090,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1137,6 +1137,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF99CC00"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1204,7 +1210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1281,6 +1287,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4260,7 +4269,7 @@
       <c r="AK30" s="9"/>
       <c r="AL30" s="9"/>
     </row>
-    <row r="31" spans="1:38" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>415</v>
       </c>
@@ -4365,7 +4374,7 @@
       <c r="AL31" s="9"/>
     </row>
     <row r="32" spans="1:38" ht="388.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9">
+      <c r="A32" s="28">
         <v>416</v>
       </c>
       <c r="B32" s="10">
@@ -8014,7 +8023,7 @@
       <c r="AK70" s="9"/>
       <c r="AL70" s="9"/>
     </row>
-    <row r="71" spans="1:38" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:38" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>461</v>
       </c>
@@ -8102,7 +8111,7 @@
       <c r="AK71" s="9"/>
       <c r="AL71" s="9"/>
     </row>
-    <row r="72" spans="1:38" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:38" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>462</v>
       </c>
@@ -8197,7 +8206,7 @@
   <autoFilter ref="A8:AL72" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="6">
       <filters>
-        <filter val="1 - Gestión de la Responsabilidad Social_x000a_"/>
+        <filter val="1 - Planificación POLISIGS_x000a_"/>
       </filters>
     </filterColumn>
     <filterColumn colId="10">

--- a/data/raw/OM.xlsx
+++ b/data/raw/OM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_0D12FA7D2C23FC90E8E5190A719AB67B9AC88E26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6851D289-20E8-4263-8B1F-4D15D6F25DE6}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_0D12FA7D2C23FC90E8E5190A719AB67B9AC88E26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EBB9091-E4C6-4D5C-ABF0-93DFB7EC83F0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$8:$AL$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4269,7 +4282,7 @@
       <c r="AK30" s="9"/>
       <c r="AL30" s="9"/>
     </row>
-    <row r="31" spans="1:38" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>415</v>
       </c>
@@ -4373,7 +4386,7 @@
       <c r="AK31" s="9"/>
       <c r="AL31" s="9"/>
     </row>
-    <row r="32" spans="1:38" ht="388.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A32" s="28">
         <v>416</v>
       </c>
@@ -8206,7 +8219,7 @@
   <autoFilter ref="A8:AL72" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="6">
       <filters>
-        <filter val="1 - Planificación POLISIGS_x000a_"/>
+        <filter val="1 - Gestión de calidad_x000a_"/>
       </filters>
     </filterColumn>
     <filterColumn colId="10">
